--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05155</v>
+        <v>-0.03915</v>
       </c>
       <c r="E2">
-        <v>-0.11505</v>
+        <v>-0.048445</v>
       </c>
       <c r="G2">
-        <v>0.0767195767195767</v>
+        <v>0.04376367614879648</v>
       </c>
       <c r="H2">
-        <v>0.0767195767195767</v>
+        <v>0.04376367614879648</v>
       </c>
       <c r="I2">
-        <v>-0.1031746031746032</v>
+        <v>0.03911378555798687</v>
       </c>
       <c r="J2">
-        <v>-0.1031746031746032</v>
+        <v>0.03911378555798687</v>
       </c>
       <c r="K2">
-        <v>417.84</v>
+        <v>166.19</v>
       </c>
       <c r="L2">
-        <v>1.228218694885362</v>
+        <v>0.4545678336980306</v>
       </c>
       <c r="M2">
-        <v>100.45</v>
+        <v>270.67</v>
       </c>
       <c r="N2">
-        <v>0.01260683492513711</v>
+        <v>0.05791962680818283</v>
       </c>
       <c r="O2">
-        <v>0.2404030250813708</v>
+        <v>1.628678019134725</v>
       </c>
       <c r="P2">
-        <v>81.18000000000001</v>
+        <v>234.77</v>
       </c>
       <c r="Q2">
-        <v>0.01018838087827408</v>
+        <v>0.05023752460840538</v>
       </c>
       <c r="R2">
-        <v>0.1942848937392303</v>
+        <v>1.412660208195439</v>
       </c>
       <c r="S2">
-        <v>19.27</v>
+        <v>35.9</v>
       </c>
       <c r="T2">
-        <v>0.1918367346938775</v>
+        <v>0.1326338345586877</v>
       </c>
       <c r="U2">
-        <v>809.49</v>
+        <v>584.72</v>
       </c>
       <c r="V2">
-        <v>0.1015938955057167</v>
+        <v>0.1251219720962082</v>
       </c>
       <c r="W2">
-        <v>0.1055483870967742</v>
+        <v>0.02506541077969649</v>
       </c>
       <c r="X2">
-        <v>0.02704536585981518</v>
+        <v>0.06009288866960037</v>
       </c>
       <c r="Y2">
-        <v>0.07850302123695901</v>
+        <v>-0.03502747788990387</v>
       </c>
       <c r="Z2">
-        <v>0.09080911401054902</v>
+        <v>0.09040598618192969</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02075762376695052</v>
+        <v>0.05779989824250001</v>
       </c>
       <c r="AC2">
-        <v>-0.02075762376695052</v>
+        <v>-0.05847354621086766</v>
       </c>
       <c r="AD2">
-        <v>1968.5</v>
+        <v>1615</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1968.5</v>
+        <v>1615</v>
       </c>
       <c r="AG2">
-        <v>1159.01</v>
+        <v>1030.28</v>
       </c>
       <c r="AH2">
-        <v>0.1981099794694255</v>
+        <v>0.2568302534906651</v>
       </c>
       <c r="AI2">
-        <v>0.3046411934939722</v>
+        <v>0.2617376788810917</v>
       </c>
       <c r="AJ2">
-        <v>0.1269882139738422</v>
+        <v>0.1806405913582585</v>
       </c>
       <c r="AK2">
-        <v>0.2050543061917374</v>
+        <v>0.184453539292249</v>
       </c>
       <c r="AL2">
-        <v>28.135</v>
+        <v>33.70699999999999</v>
       </c>
       <c r="AM2">
-        <v>-246.765</v>
+        <v>-116.693</v>
       </c>
       <c r="AN2">
-        <v>-172.6754385964913</v>
+        <v>44.00544959128066</v>
       </c>
       <c r="AO2">
-        <v>-1.247556424382442</v>
+        <v>0.4242442222683717</v>
       </c>
       <c r="AP2">
-        <v>-101.6675438596491</v>
+        <v>28.07302452316076</v>
       </c>
       <c r="AQ2">
-        <v>0.1422405932770044</v>
+        <v>-0.1225437686922095</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dubai Financial Market (DFM) P.J.S.C (DFM:DFM)</t>
+          <t>Dubai Financial Market P.J.S.C. (DFM:DFM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0815</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.217</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G3">
-        <v>0.853410740203193</v>
+        <v>0.4875</v>
       </c>
       <c r="H3">
-        <v>0.853410740203193</v>
+        <v>0.4875</v>
       </c>
       <c r="I3">
-        <v>0.2148040638606676</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="J3">
-        <v>0.2148040638606676</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="K3">
-        <v>15.2</v>
+        <v>42.1</v>
       </c>
       <c r="L3">
-        <v>0.2206095791001451</v>
+        <v>0.4385416666666667</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>192.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05850141462079037</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>4.567695961995249</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>192.3</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05850141462079037</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>4.567695961995249</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>354.2</v>
+        <v>320.7</v>
       </c>
       <c r="V3">
-        <v>0.05729166666666667</v>
+        <v>0.09756320160627908</v>
       </c>
       <c r="W3">
-        <v>0.007229144868258347</v>
+        <v>0.01977175597614239</v>
       </c>
       <c r="X3">
-        <v>0.02390931473700517</v>
+        <v>0.04951569487730093</v>
       </c>
       <c r="Y3">
-        <v>-0.01668016986874682</v>
+        <v>-0.02974393890115853</v>
       </c>
       <c r="Z3">
-        <v>0.07536644060380661</v>
+        <v>0.09552238805970149</v>
       </c>
       <c r="AA3">
-        <v>0.01618901772041129</v>
+        <v>0.04129353233830846</v>
       </c>
       <c r="AB3">
-        <v>0.02388847387100587</v>
+        <v>0.04955447929562405</v>
       </c>
       <c r="AC3">
-        <v>-0.007699456150594579</v>
+        <v>-0.008260946957315593</v>
       </c>
       <c r="AD3">
-        <v>13.7</v>
+        <v>11.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.7</v>
+        <v>11.1</v>
       </c>
       <c r="AG3">
-        <v>-340.5</v>
+        <v>-309.6</v>
       </c>
       <c r="AH3">
-        <v>0.002211068252610513</v>
+        <v>0.003365472075677643</v>
       </c>
       <c r="AI3">
-        <v>0.006375354832705106</v>
+        <v>0.005129152996626773</v>
       </c>
       <c r="AJ3">
-        <v>-0.05828583166435578</v>
+        <v>-0.1039798488664987</v>
       </c>
       <c r="AK3">
-        <v>-0.1897253022789324</v>
+        <v>-0.167950526201584</v>
       </c>
       <c r="AL3">
-        <v>0.9350000000000001</v>
+        <v>0.407</v>
       </c>
       <c r="AM3">
-        <v>0.9350000000000001</v>
+        <v>0.407</v>
       </c>
       <c r="AN3">
-        <v>0.4041297935103245</v>
+        <v>0.1840796019900497</v>
       </c>
       <c r="AO3">
-        <v>15.82887700534759</v>
+        <v>101.965601965602</v>
       </c>
       <c r="AP3">
-        <v>-10.04424778761062</v>
+        <v>-5.134328358208955</v>
       </c>
       <c r="AQ3">
-        <v>15.82887700534759</v>
+        <v>101.965601965602</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Finance House P.J.S.C. (ADX:FH)</t>
+          <t>Amlak Finance PJSC (DFM:AMLAK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,10 +856,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0216</v>
+        <v>-0.141</v>
       </c>
       <c r="E4">
-        <v>-0.214</v>
+        <v>0.57</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,85 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.24</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L4">
-        <v>0.06492985971943889</v>
+        <v>2.189010989010989</v>
       </c>
       <c r="M4">
-        <v>6.58</v>
+        <v>23.1</v>
       </c>
       <c r="N4">
-        <v>0.04044253226797788</v>
+        <v>0.09123222748815167</v>
       </c>
       <c r="O4">
-        <v>2.030864197530864</v>
+        <v>0.2319277108433735</v>
       </c>
       <c r="P4">
-        <v>6.58</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04044253226797788</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>2.030864197530864</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>2.39</v>
+        <v>46.5</v>
       </c>
       <c r="V4">
-        <v>0.01468961278426552</v>
+        <v>0.1836492890995261</v>
       </c>
       <c r="W4">
-        <v>0.0176278563656148</v>
+        <v>0.3030118649224217</v>
       </c>
       <c r="X4">
-        <v>0.02704536585981518</v>
+        <v>0.05205252851107001</v>
       </c>
       <c r="Y4">
-        <v>-0.00941750949420038</v>
+        <v>0.2509593364113517</v>
       </c>
       <c r="Z4">
-        <v>0.1730115803342347</v>
+        <v>0.1419656786271451</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02056554921387203</v>
+        <v>0.05453511974116057</v>
       </c>
       <c r="AC4">
-        <v>-0.02056554921387203</v>
+        <v>-0.05453511974116057</v>
       </c>
       <c r="AD4">
-        <v>129.2</v>
+        <v>61</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>129.2</v>
+        <v>61</v>
       </c>
       <c r="AG4">
-        <v>126.81</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>0.4426173347036657</v>
+        <v>0.1941438574156588</v>
       </c>
       <c r="AI4">
-        <v>0.3708381171067738</v>
+        <v>0.1360392506690455</v>
       </c>
       <c r="AJ4">
-        <v>0.4380159579979966</v>
+        <v>0.05416511019798282</v>
       </c>
       <c r="AK4">
-        <v>0.366492297910465</v>
+        <v>0.03607862652401095</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -987,85 +990,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>40.9</v>
+        <v>-56.9</v>
       </c>
       <c r="L5">
-        <v>0.4216494845360825</v>
+        <v>-0.5989473684210526</v>
       </c>
       <c r="M5">
-        <v>45.97</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.09747667514843086</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.123960880195599</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>44.6</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.09457167090754877</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.090464547677262</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.369999999999997</v>
-      </c>
-      <c r="T5">
-        <v>0.02980204481183375</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>94.2</v>
+        <v>27.6</v>
       </c>
       <c r="V5">
-        <v>0.1997455470737914</v>
+        <v>0.09474768280123584</v>
       </c>
       <c r="W5">
-        <v>0.1055483870967742</v>
+        <v>-0.1343882853094001</v>
       </c>
       <c r="X5">
-        <v>0.02927995238460097</v>
+        <v>0.06679874555677709</v>
       </c>
       <c r="Y5">
-        <v>0.07626843471217322</v>
+        <v>-0.2011870308661772</v>
       </c>
       <c r="Z5">
-        <v>0.1321705954489713</v>
+        <v>0.1373030784795491</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02075762376695052</v>
+        <v>0.05847354621086766</v>
       </c>
       <c r="AC5">
-        <v>-0.02075762376695052</v>
+        <v>-0.05847354621086766</v>
       </c>
       <c r="AD5">
-        <v>640.6</v>
+        <v>472.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>640.6</v>
+        <v>472.4</v>
       </c>
       <c r="AG5">
-        <v>546.4</v>
+        <v>444.8</v>
       </c>
       <c r="AH5">
-        <v>0.5759755439669124</v>
+        <v>0.6185675003273536</v>
       </c>
       <c r="AI5">
-        <v>0.5360220902016568</v>
+        <v>0.5255896751223854</v>
       </c>
       <c r="AJ5">
-        <v>0.5367387033398821</v>
+        <v>0.6042657247656569</v>
       </c>
       <c r="AK5">
-        <v>0.4963211917522027</v>
+        <v>0.5105601469237833</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amlak Finance PJSC (DFM:AMLAK)</t>
+          <t>Finance House P.J.S.C. (ADX:FH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.264</v>
+        <v>-0.0289</v>
       </c>
       <c r="E6">
-        <v>0.397</v>
+        <v>-0.146</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>230.8</v>
+        <v>4.79</v>
       </c>
       <c r="L6">
-        <v>5.56144578313253</v>
+        <v>0.09560878243512974</v>
       </c>
       <c r="M6">
-        <v>17.9</v>
+        <v>17.47</v>
       </c>
       <c r="N6">
-        <v>0.06061632238401625</v>
+        <v>0.1085767557489124</v>
       </c>
       <c r="O6">
-        <v>0.07755632582322355</v>
+        <v>3.647181628392484</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>4.67</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02902423865755127</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.9749478079331941</v>
       </c>
       <c r="S6">
-        <v>17.9</v>
+        <v>12.8</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0.7326846021751574</v>
       </c>
       <c r="U6">
-        <v>68.5</v>
+        <v>2.72</v>
       </c>
       <c r="V6">
-        <v>0.2319674906874365</v>
+        <v>0.01690490988191423</v>
       </c>
       <c r="W6">
-        <v>1.743202416918429</v>
+        <v>0.02506541077969649</v>
       </c>
       <c r="X6">
-        <v>0.02470921700544304</v>
+        <v>0.06009288866960037</v>
       </c>
       <c r="Y6">
-        <v>1.718493199912986</v>
+        <v>-0.03502747788990387</v>
       </c>
       <c r="Z6">
-        <v>0.3669319186560565</v>
+        <v>0.1585041761579347</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02297523552066581</v>
+        <v>0.06245899974193869</v>
       </c>
       <c r="AC6">
-        <v>-0.02297523552066581</v>
+        <v>-0.06245899974193869</v>
       </c>
       <c r="AD6">
-        <v>60.3</v>
+        <v>159.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>60.3</v>
+        <v>159.9</v>
       </c>
       <c r="AG6">
-        <v>-8.200000000000003</v>
+        <v>157.18</v>
       </c>
       <c r="AH6">
-        <v>0.1695725534308211</v>
+        <v>0.4984413965087282</v>
       </c>
       <c r="AI6">
-        <v>0.155012853470437</v>
+        <v>0.4346289752650177</v>
       </c>
       <c r="AJ6">
-        <v>-0.02856147683733891</v>
+        <v>0.4941524144869215</v>
       </c>
       <c r="AK6">
-        <v>-0.02558502340093605</v>
+        <v>0.4304178761158881</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,46 +1213,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0108</v>
+        <v>-0.0238</v>
       </c>
       <c r="E7">
-        <v>-0.0161</v>
+        <v>-0.00409</v>
       </c>
       <c r="G7">
-        <v>-0.3944511459589867</v>
+        <v>-0.389873417721519</v>
       </c>
       <c r="H7">
-        <v>-0.3944511459589867</v>
+        <v>-0.389873417721519</v>
       </c>
       <c r="I7">
-        <v>-0.6019300361881784</v>
+        <v>-0.3443037974683544</v>
       </c>
       <c r="J7">
-        <v>-0.6019300361881784</v>
+        <v>-0.3443037974683544</v>
       </c>
       <c r="K7">
-        <v>127.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L7">
-        <v>1.540410132689988</v>
+        <v>0.9696202531645569</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>37.8</v>
       </c>
       <c r="N7">
-        <v>0.03505082369435682</v>
+        <v>0.05553107095636844</v>
       </c>
       <c r="O7">
-        <v>0.2349256068911511</v>
+        <v>0.4934725848563969</v>
       </c>
       <c r="P7">
-        <v>30</v>
+        <v>37.8</v>
       </c>
       <c r="Q7">
-        <v>0.03505082369435682</v>
+        <v>0.05553107095636844</v>
       </c>
       <c r="R7">
-        <v>0.2349256068911511</v>
+        <v>0.4934725848563969</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1261,73 +1261,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>290.2</v>
+        <v>187.2</v>
       </c>
       <c r="V7">
-        <v>0.3390583012034116</v>
+        <v>0.2750110180696342</v>
       </c>
       <c r="W7">
-        <v>0.1633619035435589</v>
+        <v>0.08744292237442922</v>
       </c>
       <c r="X7">
-        <v>0.02910451697703348</v>
+        <v>0.06376620774875079</v>
       </c>
       <c r="Y7">
-        <v>0.1342573865665254</v>
+        <v>0.02367671462567843</v>
       </c>
       <c r="Z7">
-        <v>0.04885955089290978</v>
+        <v>0.0461853259280912</v>
       </c>
       <c r="AA7">
-        <v>-0.02941003123710733</v>
+        <v>-0.01590178310435545</v>
       </c>
       <c r="AB7">
-        <v>0.01962189641881713</v>
+        <v>0.05779989824250001</v>
       </c>
       <c r="AC7">
-        <v>-0.04903192765592446</v>
+        <v>-0.07370168134685545</v>
       </c>
       <c r="AD7">
-        <v>1124.7</v>
+        <v>910.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1124.7</v>
+        <v>910.6</v>
       </c>
       <c r="AG7">
-        <v>834.5</v>
+        <v>723.4000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.5678582247803696</v>
+        <v>0.5722365361653993</v>
       </c>
       <c r="AI7">
-        <v>0.4725034659496702</v>
+        <v>0.3974510060669548</v>
       </c>
       <c r="AJ7">
-        <v>0.4936701372456223</v>
+        <v>0.5152054696958906</v>
       </c>
       <c r="AK7">
-        <v>0.3992631931486532</v>
+        <v>0.3438376348685774</v>
       </c>
       <c r="AL7">
-        <v>27.2</v>
+        <v>33.3</v>
       </c>
       <c r="AM7">
-        <v>-247.7</v>
+        <v>-117.1</v>
       </c>
       <c r="AN7">
-        <v>-24.82781456953643</v>
+        <v>-38.58474576271186</v>
       </c>
       <c r="AO7">
-        <v>-1.834558823529412</v>
+        <v>-0.8168168168168168</v>
       </c>
       <c r="AP7">
-        <v>-18.42163355408389</v>
+        <v>-30.65254237288136</v>
       </c>
       <c r="AQ7">
-        <v>0.2014533710133226</v>
+        <v>0.2322801024765158</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.03915</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.048445</v>
+        <v>0.02465</v>
+      </c>
+      <c r="F2">
+        <v>0.29</v>
       </c>
       <c r="G2">
-        <v>0.04376367614879648</v>
+        <v>0.1971578947368421</v>
       </c>
       <c r="H2">
-        <v>0.04376367614879648</v>
+        <v>0.1971578947368421</v>
       </c>
       <c r="I2">
-        <v>0.03911378555798687</v>
+        <v>0.1833892423366107</v>
       </c>
       <c r="J2">
-        <v>0.03911378555798687</v>
+        <v>0.1791372740163063</v>
       </c>
       <c r="K2">
-        <v>166.19</v>
+        <v>333.5</v>
       </c>
       <c r="L2">
-        <v>0.4545678336980306</v>
+        <v>0.3857721226142279</v>
       </c>
       <c r="M2">
-        <v>270.67</v>
+        <v>401.29</v>
       </c>
       <c r="N2">
-        <v>0.05791962680818283</v>
+        <v>0.04084376590330789</v>
       </c>
       <c r="O2">
-        <v>1.628678019134725</v>
+        <v>1.203268365817092</v>
       </c>
       <c r="P2">
-        <v>234.77</v>
+        <v>289.49</v>
       </c>
       <c r="Q2">
-        <v>0.05023752460840538</v>
+        <v>0.029464631043257</v>
       </c>
       <c r="R2">
-        <v>1.412660208195439</v>
+        <v>0.8680359820089956</v>
       </c>
       <c r="S2">
-        <v>35.9</v>
+        <v>111.8</v>
       </c>
       <c r="T2">
-        <v>0.1326338345586877</v>
+        <v>0.2786015101298313</v>
       </c>
       <c r="U2">
-        <v>584.72</v>
+        <v>886.755</v>
       </c>
       <c r="V2">
-        <v>0.1251219720962082</v>
+        <v>0.09025496183206107</v>
       </c>
       <c r="W2">
-        <v>0.02506541077969649</v>
+        <v>0.1315957787016309</v>
       </c>
       <c r="X2">
-        <v>0.06009288866960037</v>
+        <v>0.0527935308778897</v>
       </c>
       <c r="Y2">
-        <v>-0.03502747788990387</v>
+        <v>0.07880224782374125</v>
       </c>
       <c r="Z2">
-        <v>0.09040598618192969</v>
+        <v>0.2129895279122222</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05779989824250001</v>
+        <v>0.0515462371428773</v>
       </c>
       <c r="AC2">
-        <v>-0.05847354621086766</v>
+        <v>-0.05156794658773751</v>
       </c>
       <c r="AD2">
-        <v>1615</v>
+        <v>2159.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1615</v>
+        <v>2159.7</v>
       </c>
       <c r="AG2">
-        <v>1030.28</v>
+        <v>1272.945</v>
       </c>
       <c r="AH2">
-        <v>0.2568302534906651</v>
+        <v>0.1802047610703647</v>
       </c>
       <c r="AI2">
-        <v>0.2617376788810917</v>
+        <v>0.2782688244085966</v>
       </c>
       <c r="AJ2">
-        <v>0.1806405913582585</v>
+        <v>0.1147009649083681</v>
       </c>
       <c r="AK2">
-        <v>0.184453539292249</v>
+        <v>0.1851705846799269</v>
       </c>
       <c r="AL2">
-        <v>33.70699999999999</v>
+        <v>88.63</v>
       </c>
       <c r="AM2">
-        <v>-116.693</v>
+        <v>-122.595</v>
       </c>
       <c r="AN2">
-        <v>44.00544959128066</v>
+        <v>11.11585773843224</v>
       </c>
       <c r="AO2">
-        <v>0.4242442222683717</v>
+        <v>1.788784835834368</v>
       </c>
       <c r="AP2">
-        <v>28.07302452316076</v>
+        <v>6.551778269596993</v>
       </c>
       <c r="AQ2">
-        <v>-0.1225437686922095</v>
+        <v>-1.293201190913169</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dubai Financial Market P.J.S.C. (DFM:DFM)</t>
+          <t>Network International Holdings plc (LSE:NETW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +724,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.04940000000000001</v>
-      </c>
-      <c r="E3">
-        <v>-0.09279999999999999</v>
+      <c r="F3">
+        <v>0.29</v>
       </c>
       <c r="G3">
-        <v>0.4875</v>
+        <v>0.2862886161658909</v>
       </c>
       <c r="H3">
-        <v>0.4875</v>
+        <v>0.2862886161658909</v>
       </c>
       <c r="I3">
-        <v>0.4322916666666667</v>
+        <v>0.2848074481591197</v>
       </c>
       <c r="J3">
-        <v>0.4322916666666667</v>
+        <v>0.2385836586897465</v>
       </c>
       <c r="K3">
-        <v>42.1</v>
+        <v>82.3</v>
       </c>
       <c r="L3">
-        <v>0.4385416666666667</v>
+        <v>0.1741430385103682</v>
       </c>
       <c r="M3">
-        <v>192.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.05850141462079037</v>
+        <v>0.03587630424920611</v>
       </c>
       <c r="O3">
-        <v>4.567695961995249</v>
+        <v>1.153098420413123</v>
       </c>
       <c r="P3">
-        <v>192.3</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.05850141462079037</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>4.567695961995249</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>320.7</v>
+        <v>150</v>
       </c>
       <c r="V3">
-        <v>0.09756320160627908</v>
+        <v>0.05670648722213822</v>
       </c>
       <c r="W3">
-        <v>0.01977175597614239</v>
+        <v>0.1315957787016309</v>
       </c>
       <c r="X3">
-        <v>0.04951569487730093</v>
+        <v>0.05300519750539607</v>
       </c>
       <c r="Y3">
-        <v>-0.02974393890115853</v>
+        <v>0.07859058119623488</v>
       </c>
       <c r="Z3">
-        <v>0.09552238805970149</v>
+        <v>1.44437652811736</v>
       </c>
       <c r="AA3">
-        <v>0.04129353233830846</v>
+        <v>0.3446046366038331</v>
       </c>
       <c r="AB3">
-        <v>0.04955447929562405</v>
+        <v>0.05157114288896156</v>
       </c>
       <c r="AC3">
-        <v>-0.008260946957315593</v>
+        <v>0.2930334937148715</v>
       </c>
       <c r="AD3">
-        <v>11.1</v>
+        <v>403.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.1</v>
+        <v>403.7</v>
       </c>
       <c r="AG3">
-        <v>-309.6</v>
+        <v>253.7</v>
       </c>
       <c r="AH3">
-        <v>0.003365472075677643</v>
+        <v>0.1324084095903441</v>
       </c>
       <c r="AI3">
-        <v>0.005129152996626773</v>
+        <v>0.4020515884872025</v>
       </c>
       <c r="AJ3">
-        <v>-0.1039798488664987</v>
+        <v>0.08751595432750355</v>
       </c>
       <c r="AK3">
-        <v>-0.167950526201584</v>
+        <v>0.2970378175857628</v>
       </c>
       <c r="AL3">
-        <v>0.407</v>
+        <v>26.3</v>
       </c>
       <c r="AM3">
-        <v>0.407</v>
+        <v>24.6</v>
       </c>
       <c r="AN3">
-        <v>0.1840796019900497</v>
+        <v>2.636838667537557</v>
       </c>
       <c r="AO3">
-        <v>101.965601965602</v>
+        <v>5.11787072243346</v>
       </c>
       <c r="AP3">
-        <v>-5.134328358208955</v>
+        <v>1.657086871325931</v>
       </c>
       <c r="AQ3">
-        <v>101.965601965602</v>
+        <v>5.471544715447154</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amlak Finance PJSC (DFM:AMLAK)</t>
+          <t>Dubai Financial Market P.J.S.C. (DFM:DFM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,109 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.141</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="E4">
-        <v>0.57</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.4543325526932085</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.4543325526932085</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.5183450429352069</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.5183450429352069</v>
       </c>
       <c r="K4">
-        <v>99.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="L4">
-        <v>2.189010989010989</v>
+        <v>0.5191256830601093</v>
       </c>
       <c r="M4">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
       <c r="N4">
-        <v>0.09123222748815167</v>
+        <v>0.01239218796470705</v>
       </c>
       <c r="O4">
-        <v>0.2319277108433735</v>
+        <v>0.5639097744360902</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>37.5</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01239218796470705</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5639097744360902</v>
       </c>
       <c r="S4">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>46.5</v>
+        <v>188</v>
       </c>
       <c r="V4">
-        <v>0.1836492890995261</v>
+        <v>0.06212616899639801</v>
       </c>
       <c r="W4">
-        <v>0.3030118649224217</v>
+        <v>0.03095614933432642</v>
       </c>
       <c r="X4">
-        <v>0.05205252851107001</v>
+        <v>0.05157814380371378</v>
       </c>
       <c r="Y4">
-        <v>0.2509593364113517</v>
+        <v>-0.02062199446938737</v>
       </c>
       <c r="Z4">
-        <v>0.1419656786271451</v>
+        <v>0.1214333112143332</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.06294435491515786</v>
       </c>
       <c r="AB4">
-        <v>0.05453511974116057</v>
+        <v>0.05153236252623982</v>
       </c>
       <c r="AC4">
-        <v>-0.05453511974116057</v>
+        <v>0.01141199238891804</v>
       </c>
       <c r="AD4">
-        <v>61</v>
+        <v>10.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>61</v>
+        <v>10.1</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>-177.9</v>
       </c>
       <c r="AH4">
-        <v>0.1941438574156588</v>
+        <v>0.003326526579276728</v>
       </c>
       <c r="AI4">
-        <v>0.1360392506690455</v>
+        <v>0.004576140637035023</v>
       </c>
       <c r="AJ4">
-        <v>0.05416511019798282</v>
+        <v>-0.06246050136928587</v>
       </c>
       <c r="AK4">
-        <v>0.03607862652401095</v>
+        <v>-0.0881085632212372</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.025</v>
+      </c>
+      <c r="AN4">
+        <v>0.1191037735849057</v>
+      </c>
+      <c r="AP4">
+        <v>-2.097877358490566</v>
+      </c>
+      <c r="AQ4">
+        <v>-2656</v>
       </c>
     </row>
     <row r="5">
@@ -977,95 +986,83 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
-        <v>-56.9</v>
-      </c>
-      <c r="L5">
-        <v>-0.5989473684210526</v>
+        <v>-152.7</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>6.79</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0472841225626741</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.04446627373935822</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>6.79</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0472841225626741</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0.04446627373935822</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>27.6</v>
+        <v>28.9</v>
       </c>
       <c r="V5">
-        <v>0.09474768280123584</v>
+        <v>0.2012534818941504</v>
       </c>
       <c r="W5">
-        <v>-0.1343882853094001</v>
+        <v>-0.4600783368484483</v>
       </c>
       <c r="X5">
-        <v>0.06679874555677709</v>
+        <v>0.07223002481849694</v>
       </c>
       <c r="Y5">
-        <v>-0.2011870308661772</v>
+        <v>-0.5323083616669453</v>
       </c>
       <c r="Z5">
-        <v>0.1373030784795491</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05847354621086766</v>
+        <v>0.0486937183731707</v>
       </c>
       <c r="AC5">
-        <v>-0.05847354621086766</v>
+        <v>-0.0486937183731707</v>
       </c>
       <c r="AD5">
-        <v>472.4</v>
+        <v>310.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>472.4</v>
+        <v>310.7</v>
       </c>
       <c r="AG5">
-        <v>444.8</v>
+        <v>281.8</v>
       </c>
       <c r="AH5">
-        <v>0.6185675003273536</v>
+        <v>0.6839093110279552</v>
       </c>
       <c r="AI5">
-        <v>0.5255896751223854</v>
+        <v>0.6181854357341822</v>
       </c>
       <c r="AJ5">
-        <v>0.6042657247656569</v>
+        <v>0.6624353549600377</v>
       </c>
       <c r="AK5">
-        <v>0.5105601469237833</v>
+        <v>0.594891281401731</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finance House P.J.S.C. (ADX:FH)</t>
+          <t>Amlak Finance PJSC (DFM:AMLAK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,10 +1088,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0289</v>
-      </c>
-      <c r="E6">
-        <v>-0.146</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1103,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>4.79</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L6">
-        <v>0.09560878243512974</v>
+        <v>1.743682310469314</v>
       </c>
       <c r="M6">
-        <v>17.47</v>
+        <v>16.9</v>
       </c>
       <c r="N6">
-        <v>0.1085767557489124</v>
+        <v>0.05139902676399026</v>
       </c>
       <c r="O6">
-        <v>3.647181628392484</v>
+        <v>0.1749482401656315</v>
       </c>
       <c r="P6">
-        <v>4.67</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02902423865755127</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.9749478079331941</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>12.8</v>
+        <v>16.9</v>
       </c>
       <c r="T6">
-        <v>0.7326846021751574</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>58.5</v>
       </c>
       <c r="V6">
-        <v>0.01690490988191423</v>
+        <v>0.1779197080291971</v>
       </c>
       <c r="W6">
-        <v>0.02506541077969649</v>
+        <v>0.2493546721734641</v>
       </c>
       <c r="X6">
-        <v>0.06009288866960037</v>
+        <v>0.0527935308778897</v>
       </c>
       <c r="Y6">
-        <v>-0.03502747788990387</v>
+        <v>0.1965611412955744</v>
       </c>
       <c r="Z6">
-        <v>0.1585041761579347</v>
+        <v>0.1378452351331177</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06245899974193869</v>
+        <v>0.05156794658773751</v>
       </c>
       <c r="AC6">
-        <v>-0.06245899974193869</v>
+        <v>-0.05156794658773751</v>
       </c>
       <c r="AD6">
-        <v>159.9</v>
+        <v>42.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>159.9</v>
+        <v>42.9</v>
       </c>
       <c r="AG6">
-        <v>157.18</v>
+        <v>-15.6</v>
       </c>
       <c r="AH6">
-        <v>0.4984413965087282</v>
+        <v>0.1154156577885391</v>
       </c>
       <c r="AI6">
-        <v>0.4346289752650177</v>
+        <v>0.08807226442208993</v>
       </c>
       <c r="AJ6">
-        <v>0.4941524144869215</v>
+        <v>-0.04980842911877395</v>
       </c>
       <c r="AK6">
-        <v>0.4304178761158881</v>
+        <v>-0.03639757349510033</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,130 +1198,347 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>E7 Group PJSC (ADX:E7)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-12</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.255</v>
+      </c>
+      <c r="V7">
+        <v>0.0004205838693715982</v>
+      </c>
+      <c r="W7">
+        <v>1.886792452830188</v>
+      </c>
+      <c r="X7">
+        <v>0.0515462371428773</v>
+      </c>
+      <c r="Y7">
+        <v>1.835246215687311</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-0.0143496790203377</v>
+      </c>
+      <c r="AB7">
+        <v>0.0515462371428773</v>
+      </c>
+      <c r="AC7">
+        <v>-0.065895916163215</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-0.255</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.0004207608345914908</v>
+      </c>
+      <c r="AK7">
+        <v>0.01776384535005225</v>
+      </c>
+      <c r="AL7">
+        <v>12.6</v>
+      </c>
+      <c r="AM7">
+        <v>12.6</v>
+      </c>
+      <c r="AO7">
+        <v>-0.1055555555555556</v>
+      </c>
+      <c r="AQ7">
+        <v>-0.1055555555555556</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Al Waha Capital PJSC (ADX:WAHA)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.0238</v>
-      </c>
-      <c r="E7">
-        <v>-0.00409</v>
-      </c>
-      <c r="G7">
-        <v>-0.389873417721519</v>
-      </c>
-      <c r="H7">
-        <v>-0.389873417721519</v>
-      </c>
-      <c r="I7">
-        <v>-0.3443037974683544</v>
-      </c>
-      <c r="J7">
-        <v>-0.3443037974683544</v>
-      </c>
-      <c r="K7">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="L7">
-        <v>0.9696202531645569</v>
-      </c>
-      <c r="M7">
-        <v>37.8</v>
-      </c>
-      <c r="N7">
-        <v>0.05553107095636844</v>
-      </c>
-      <c r="O7">
-        <v>0.4934725848563969</v>
-      </c>
-      <c r="P7">
-        <v>37.8</v>
-      </c>
-      <c r="Q7">
-        <v>0.05553107095636844</v>
-      </c>
-      <c r="R7">
-        <v>0.4934725848563969</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>187.2</v>
-      </c>
-      <c r="V7">
-        <v>0.2750110180696342</v>
-      </c>
-      <c r="W7">
-        <v>0.08744292237442922</v>
-      </c>
-      <c r="X7">
-        <v>0.06376620774875079</v>
-      </c>
-      <c r="Y7">
-        <v>0.02367671462567843</v>
-      </c>
-      <c r="Z7">
-        <v>0.0461853259280912</v>
-      </c>
-      <c r="AA7">
-        <v>-0.01590178310435545</v>
-      </c>
-      <c r="AB7">
-        <v>0.05779989824250001</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07370168134685545</v>
-      </c>
-      <c r="AD7">
-        <v>910.6</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>910.6</v>
-      </c>
-      <c r="AG7">
-        <v>723.4000000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.5722365361653993</v>
-      </c>
-      <c r="AI7">
-        <v>0.3974510060669548</v>
-      </c>
-      <c r="AJ7">
-        <v>0.5152054696958906</v>
-      </c>
-      <c r="AK7">
-        <v>0.3438376348685774</v>
-      </c>
-      <c r="AL7">
-        <v>33.3</v>
-      </c>
-      <c r="AM7">
-        <v>-117.1</v>
-      </c>
-      <c r="AN7">
-        <v>-38.58474576271186</v>
-      </c>
-      <c r="AO7">
-        <v>-0.8168168168168168</v>
-      </c>
-      <c r="AP7">
-        <v>-30.65254237288136</v>
-      </c>
-      <c r="AQ7">
-        <v>0.2322801024765158</v>
+      <c r="D8">
+        <v>-0.141</v>
+      </c>
+      <c r="E8">
+        <v>-0.0347</v>
+      </c>
+      <c r="G8">
+        <v>-0.6556473829201103</v>
+      </c>
+      <c r="H8">
+        <v>-0.6556473829201103</v>
+      </c>
+      <c r="I8">
+        <v>-1.088154269972452</v>
+      </c>
+      <c r="J8">
+        <v>-1.088154269972452</v>
+      </c>
+      <c r="K8">
+        <v>103.4</v>
+      </c>
+      <c r="L8">
+        <v>2.848484848484849</v>
+      </c>
+      <c r="M8">
+        <v>41</v>
+      </c>
+      <c r="N8">
+        <v>0.04503514938488577</v>
+      </c>
+      <c r="O8">
+        <v>0.3965183752417795</v>
+      </c>
+      <c r="P8">
+        <v>41</v>
+      </c>
+      <c r="Q8">
+        <v>0.04503514938488577</v>
+      </c>
+      <c r="R8">
+        <v>0.3965183752417795</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>236.9</v>
+      </c>
+      <c r="V8">
+        <v>0.2602152899824253</v>
+      </c>
+      <c r="W8">
+        <v>0.1134145003838982</v>
+      </c>
+      <c r="X8">
+        <v>0.06584795203902091</v>
+      </c>
+      <c r="Y8">
+        <v>0.04756654834487729</v>
+      </c>
+      <c r="Z8">
+        <v>0.02220047703504372</v>
+      </c>
+      <c r="AA8">
+        <v>-0.02415754388110819</v>
+      </c>
+      <c r="AB8">
+        <v>0.04904633895745128</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07320388283855947</v>
+      </c>
+      <c r="AD8">
+        <v>1362</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1362</v>
+      </c>
+      <c r="AG8">
+        <v>1125.1</v>
+      </c>
+      <c r="AH8">
+        <v>0.5993663087484598</v>
+      </c>
+      <c r="AI8">
+        <v>0.4538033518808516</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5527388847948906</v>
+      </c>
+      <c r="AK8">
+        <v>0.4069960931847779</v>
+      </c>
+      <c r="AL8">
+        <v>47</v>
+      </c>
+      <c r="AM8">
+        <v>-162.5</v>
+      </c>
+      <c r="AN8">
+        <v>-35.93667546174142</v>
+      </c>
+      <c r="AO8">
+        <v>-0.8404255319148937</v>
+      </c>
+      <c r="AP8">
+        <v>-29.68601583113456</v>
+      </c>
+      <c r="AQ8">
+        <v>0.2430769230769231</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Al Ansari Financial Services PJSC (DFM:ALANSARI)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0.00431725740848344</v>
+      </c>
+      <c r="H9">
+        <v>0.00431725740848344</v>
+      </c>
+      <c r="I9">
+        <v>-0.0094712376525276</v>
+      </c>
+      <c r="J9">
+        <v>-0.0094712376525276</v>
+      </c>
+      <c r="K9">
+        <v>149.4</v>
+      </c>
+      <c r="L9">
+        <v>0.8680999418942476</v>
+      </c>
+      <c r="M9">
+        <v>204.2</v>
+      </c>
+      <c r="N9">
+        <v>0.0943361360066525</v>
+      </c>
+      <c r="O9">
+        <v>1.366800535475234</v>
+      </c>
+      <c r="P9">
+        <v>204.2</v>
+      </c>
+      <c r="Q9">
+        <v>0.0943361360066525</v>
+      </c>
+      <c r="R9">
+        <v>1.366800535475234</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>224.2</v>
+      </c>
+      <c r="V9">
+        <v>0.1035757183775293</v>
+      </c>
+      <c r="X9">
+        <v>0.05168005320084269</v>
+      </c>
+      <c r="AB9">
+        <v>0.05157646740024477</v>
+      </c>
+      <c r="AD9">
+        <v>30.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>30.3</v>
+      </c>
+      <c r="AG9">
+        <v>-193.9</v>
+      </c>
+      <c r="AH9">
+        <v>0.01380472914483576</v>
+      </c>
+      <c r="AI9">
+        <v>0.05287035421392428</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.09839143451565434</v>
+      </c>
+      <c r="AK9">
+        <v>-0.5557466322728575</v>
+      </c>
+      <c r="AL9">
+        <v>2.73</v>
+      </c>
+      <c r="AM9">
+        <v>2.73</v>
+      </c>
+      <c r="AN9">
+        <v>-5.306479859894921</v>
+      </c>
+      <c r="AO9">
+        <v>-0.5970695970695971</v>
+      </c>
+      <c r="AP9">
+        <v>33.95796847635727</v>
+      </c>
+      <c r="AQ9">
+        <v>-0.5970695970695971</v>
       </c>
     </row>
   </sheetData>
